--- a/Design files/Right-Side/BOM/eSpark BOM-RIGHT-Bone_Conduction_Glasses.xlsx
+++ b/Design files/Right-Side/BOM/eSpark BOM-RIGHT-Bone_Conduction_Glasses.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="184">
   <si>
     <t>Component list</t>
   </si>
@@ -556,6 +556,21 @@
   </si>
   <si>
     <t>Right-Bone_Conduction_Glasses</t>
+  </si>
+  <si>
+    <t>3.7V Lithium Polymer Rechargeable Battery 501230 300mah</t>
+  </si>
+  <si>
+    <t>Battery</t>
+  </si>
+  <si>
+    <t>Aliexpress</t>
+  </si>
+  <si>
+    <t>Bone Conduction Module Sensor Deafness Dumb Mini bone conduction horn speaker (GD02)</t>
+  </si>
+  <si>
+    <t>Transducer (GD02)</t>
   </si>
 </sst>
 </file>
@@ -3200,7 +3215,7 @@
       <c r="R33" s="37"/>
       <c r="S33" s="65"/>
     </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:19" ht="30" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
       <c r="B34" s="46">
         <f t="shared" ref="B34:B35" si="21">ROW(B34) - ROW($B$9)</f>
@@ -3209,24 +3224,54 @@
       <c r="C34" s="54" t="s">
         <v>158</v>
       </c>
-      <c r="D34" s="37"/>
-      <c r="E34" s="37"/>
-      <c r="F34" s="37"/>
-      <c r="G34" s="37"/>
-      <c r="H34" s="37"/>
-      <c r="I34" s="37"/>
-      <c r="J34" s="37"/>
-      <c r="K34" s="37"/>
-      <c r="L34" s="37"/>
-      <c r="M34" s="37"/>
-      <c r="N34" s="37"/>
-      <c r="O34" s="37"/>
-      <c r="P34" s="38"/>
-      <c r="Q34" s="38"/>
+      <c r="D34" s="37" t="s">
+        <v>160</v>
+      </c>
+      <c r="E34" s="37" t="s">
+        <v>179</v>
+      </c>
+      <c r="F34" s="37" t="s">
+        <v>160</v>
+      </c>
+      <c r="G34" s="37" t="s">
+        <v>180</v>
+      </c>
+      <c r="H34" s="37" t="s">
+        <v>160</v>
+      </c>
+      <c r="I34" s="37" t="s">
+        <v>160</v>
+      </c>
+      <c r="J34" s="37" t="s">
+        <v>160</v>
+      </c>
+      <c r="K34" s="37" t="s">
+        <v>160</v>
+      </c>
+      <c r="L34" s="37">
+        <v>1</v>
+      </c>
+      <c r="M34" s="37">
+        <f>L34*5</f>
+        <v>5</v>
+      </c>
+      <c r="N34" s="37">
+        <v>10</v>
+      </c>
+      <c r="O34" s="63" t="s">
+        <v>181</v>
+      </c>
+      <c r="P34" s="38">
+        <v>0.97</v>
+      </c>
+      <c r="Q34" s="38">
+        <f>P34*N34</f>
+        <v>9.6999999999999993</v>
+      </c>
       <c r="R34" s="37"/>
       <c r="S34" s="59"/>
     </row>
-    <row r="35" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="1"/>
       <c r="B35" s="46">
         <f t="shared" si="21"/>
@@ -3235,20 +3280,50 @@
       <c r="C35" s="60" t="s">
         <v>158</v>
       </c>
-      <c r="D35" s="37"/>
-      <c r="E35" s="37"/>
-      <c r="F35" s="37"/>
-      <c r="G35" s="37"/>
-      <c r="H35" s="37"/>
-      <c r="I35" s="37"/>
-      <c r="J35" s="37"/>
-      <c r="K35" s="37"/>
-      <c r="L35" s="37"/>
-      <c r="M35" s="37"/>
-      <c r="N35" s="37"/>
-      <c r="O35" s="37"/>
-      <c r="P35" s="38"/>
-      <c r="Q35" s="38"/>
+      <c r="D35" s="37" t="s">
+        <v>160</v>
+      </c>
+      <c r="E35" s="37" t="s">
+        <v>182</v>
+      </c>
+      <c r="F35" s="37" t="s">
+        <v>160</v>
+      </c>
+      <c r="G35" s="37" t="s">
+        <v>183</v>
+      </c>
+      <c r="H35" s="37" t="s">
+        <v>160</v>
+      </c>
+      <c r="I35" s="37" t="s">
+        <v>160</v>
+      </c>
+      <c r="J35" s="37" t="s">
+        <v>160</v>
+      </c>
+      <c r="K35" s="37" t="s">
+        <v>160</v>
+      </c>
+      <c r="L35" s="37">
+        <v>1</v>
+      </c>
+      <c r="M35" s="37">
+        <f>L35*5</f>
+        <v>5</v>
+      </c>
+      <c r="N35" s="37">
+        <v>6</v>
+      </c>
+      <c r="O35" s="63" t="s">
+        <v>181</v>
+      </c>
+      <c r="P35" s="38">
+        <v>3.93</v>
+      </c>
+      <c r="Q35" s="38">
+        <f>P35*N35</f>
+        <v>23.580000000000002</v>
+      </c>
       <c r="R35" s="37"/>
       <c r="S35" s="39"/>
     </row>
@@ -3273,7 +3348,7 @@
       <c r="P36" s="77"/>
       <c r="Q36" s="48">
         <f>SUM(Q10:Q35)</f>
-        <v>117.33386</v>
+        <v>150.61386000000002</v>
       </c>
       <c r="R36" s="72"/>
       <c r="S36" s="73"/>
@@ -3299,7 +3374,7 @@
       <c r="P37" s="77"/>
       <c r="Q37" s="49">
         <f>Q36/5</f>
-        <v>23.466771999999999</v>
+        <v>30.122772000000005</v>
       </c>
       <c r="R37" s="74"/>
       <c r="S37" s="75"/>
@@ -3337,9 +3412,11 @@
     <hyperlink ref="O29" r:id="rId22"/>
     <hyperlink ref="O30" r:id="rId23"/>
     <hyperlink ref="O32" r:id="rId24"/>
+    <hyperlink ref="O34" r:id="rId25"/>
+    <hyperlink ref="O35" r:id="rId26"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId25"/>
-  <drawing r:id="rId26"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId27"/>
+  <drawing r:id="rId28"/>
 </worksheet>
 </file>
--- a/Design files/Right-Side/BOM/eSpark BOM-RIGHT-Bone_Conduction_Glasses.xlsx
+++ b/Design files/Right-Side/BOM/eSpark BOM-RIGHT-Bone_Conduction_Glasses.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="186">
   <si>
     <t>Component list</t>
   </si>
@@ -571,6 +571,12 @@
   </si>
   <si>
     <t>Transducer (GD02)</t>
+  </si>
+  <si>
+    <t>Touch Material</t>
+  </si>
+  <si>
+    <t>TO be Confirmed By Mechanical Team</t>
   </si>
 </sst>
 </file>
@@ -1609,7 +1615,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:S37"/>
+  <dimension ref="A1:S38"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3.140625" style="26" customWidth="1"/>
@@ -3218,7 +3224,7 @@
     <row r="34" spans="1:19" ht="30" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
       <c r="B34" s="46">
-        <f t="shared" ref="B34:B35" si="21">ROW(B34) - ROW($B$9)</f>
+        <f t="shared" ref="B34:B36" si="21">ROW(B34) - ROW($B$9)</f>
         <v>25</v>
       </c>
       <c r="C34" s="54" t="s">
@@ -3271,121 +3277,167 @@
       <c r="R34" s="37"/>
       <c r="S34" s="59"/>
     </row>
-    <row r="35" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A35" s="1"/>
       <c r="B35" s="46">
         <f t="shared" si="21"/>
         <v>26</v>
       </c>
-      <c r="C35" s="60" t="s">
+      <c r="C35" s="54" t="s">
         <v>158</v>
       </c>
-      <c r="D35" s="37" t="s">
-        <v>160</v>
-      </c>
-      <c r="E35" s="37" t="s">
+      <c r="D35" s="51" t="s">
+        <v>160</v>
+      </c>
+      <c r="E35" s="37"/>
+      <c r="F35" s="51" t="s">
+        <v>160</v>
+      </c>
+      <c r="G35" s="62" t="s">
+        <v>184</v>
+      </c>
+      <c r="H35" s="51" t="s">
+        <v>160</v>
+      </c>
+      <c r="I35" s="62" t="s">
+        <v>160</v>
+      </c>
+      <c r="J35" s="37" t="s">
+        <v>160</v>
+      </c>
+      <c r="K35" s="37" t="s">
+        <v>160</v>
+      </c>
+      <c r="L35" s="51">
+        <v>1</v>
+      </c>
+      <c r="M35" s="37">
+        <v>5</v>
+      </c>
+      <c r="N35" s="37"/>
+      <c r="O35" s="63"/>
+      <c r="P35" s="38"/>
+      <c r="Q35" s="38"/>
+      <c r="R35" s="37"/>
+      <c r="S35" s="67" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="1"/>
+      <c r="B36" s="46">
+        <f t="shared" si="21"/>
+        <v>27</v>
+      </c>
+      <c r="C36" s="60" t="s">
+        <v>158</v>
+      </c>
+      <c r="D36" s="37" t="s">
+        <v>160</v>
+      </c>
+      <c r="E36" s="37" t="s">
         <v>182</v>
       </c>
-      <c r="F35" s="37" t="s">
-        <v>160</v>
-      </c>
-      <c r="G35" s="37" t="s">
+      <c r="F36" s="37" t="s">
+        <v>160</v>
+      </c>
+      <c r="G36" s="37" t="s">
         <v>183</v>
       </c>
-      <c r="H35" s="37" t="s">
-        <v>160</v>
-      </c>
-      <c r="I35" s="37" t="s">
-        <v>160</v>
-      </c>
-      <c r="J35" s="37" t="s">
-        <v>160</v>
-      </c>
-      <c r="K35" s="37" t="s">
-        <v>160</v>
-      </c>
-      <c r="L35" s="37">
+      <c r="H36" s="37" t="s">
+        <v>160</v>
+      </c>
+      <c r="I36" s="37" t="s">
+        <v>160</v>
+      </c>
+      <c r="J36" s="37" t="s">
+        <v>160</v>
+      </c>
+      <c r="K36" s="37" t="s">
+        <v>160</v>
+      </c>
+      <c r="L36" s="37">
         <v>1</v>
       </c>
-      <c r="M35" s="37">
-        <f>L35*5</f>
+      <c r="M36" s="37">
+        <f>L36*5</f>
         <v>5</v>
       </c>
-      <c r="N35" s="37">
+      <c r="N36" s="37">
         <v>6</v>
       </c>
-      <c r="O35" s="63" t="s">
+      <c r="O36" s="63" t="s">
         <v>181</v>
       </c>
-      <c r="P35" s="38">
+      <c r="P36" s="38">
         <v>3.93</v>
       </c>
-      <c r="Q35" s="38">
-        <f>P35*N35</f>
+      <c r="Q36" s="38">
+        <f>P36*N36</f>
         <v>23.580000000000002</v>
       </c>
-      <c r="R35" s="37"/>
-      <c r="S35" s="39"/>
-    </row>
-    <row r="36" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="1"/>
-      <c r="B36" s="40"/>
-      <c r="C36" s="41"/>
-      <c r="D36" s="42"/>
-      <c r="E36" s="43"/>
-      <c r="F36" s="44"/>
-      <c r="G36" s="45"/>
-      <c r="H36" s="44"/>
-      <c r="I36" s="45"/>
-      <c r="J36" s="44"/>
-      <c r="K36" s="45"/>
-      <c r="L36" s="45"/>
-      <c r="M36" s="45"/>
-      <c r="N36" s="76" t="s">
-        <v>5</v>
-      </c>
-      <c r="O36" s="77"/>
-      <c r="P36" s="77"/>
-      <c r="Q36" s="48">
-        <f>SUM(Q10:Q35)</f>
-        <v>150.61386000000002</v>
-      </c>
-      <c r="R36" s="72"/>
-      <c r="S36" s="73"/>
+      <c r="R36" s="37"/>
+      <c r="S36" s="39"/>
     </row>
     <row r="37" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="1"/>
-      <c r="B37" s="25"/>
-      <c r="C37" s="36"/>
-      <c r="D37" s="9"/>
-      <c r="E37" s="10"/>
-      <c r="F37" s="10"/>
-      <c r="G37" s="10"/>
-      <c r="H37" s="10"/>
-      <c r="I37" s="10"/>
-      <c r="J37" s="10"/>
-      <c r="K37" s="10"/>
-      <c r="L37" s="10"/>
-      <c r="M37" s="10"/>
+      <c r="B37" s="40"/>
+      <c r="C37" s="41"/>
+      <c r="D37" s="42"/>
+      <c r="E37" s="43"/>
+      <c r="F37" s="44"/>
+      <c r="G37" s="45"/>
+      <c r="H37" s="44"/>
+      <c r="I37" s="45"/>
+      <c r="J37" s="44"/>
+      <c r="K37" s="45"/>
+      <c r="L37" s="45"/>
+      <c r="M37" s="45"/>
       <c r="N37" s="76" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O37" s="77"/>
       <c r="P37" s="77"/>
-      <c r="Q37" s="49">
-        <f>Q36/5</f>
+      <c r="Q37" s="48">
+        <f>SUM(Q10:Q36)</f>
+        <v>150.61386000000002</v>
+      </c>
+      <c r="R37" s="72"/>
+      <c r="S37" s="73"/>
+    </row>
+    <row r="38" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="1"/>
+      <c r="B38" s="25"/>
+      <c r="C38" s="36"/>
+      <c r="D38" s="9"/>
+      <c r="E38" s="10"/>
+      <c r="F38" s="10"/>
+      <c r="G38" s="10"/>
+      <c r="H38" s="10"/>
+      <c r="I38" s="10"/>
+      <c r="J38" s="10"/>
+      <c r="K38" s="10"/>
+      <c r="L38" s="10"/>
+      <c r="M38" s="10"/>
+      <c r="N38" s="76" t="s">
+        <v>6</v>
+      </c>
+      <c r="O38" s="77"/>
+      <c r="P38" s="77"/>
+      <c r="Q38" s="49">
+        <f>Q37/5</f>
         <v>30.122772000000005</v>
       </c>
-      <c r="R37" s="74"/>
-      <c r="S37" s="75"/>
+      <c r="R38" s="74"/>
+      <c r="S38" s="75"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="K1:S1"/>
     <mergeCell ref="S3:S8"/>
-    <mergeCell ref="R36:S37"/>
-    <mergeCell ref="N36:P36"/>
+    <mergeCell ref="R37:S38"/>
     <mergeCell ref="N37:P37"/>
+    <mergeCell ref="N38:P38"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="O12" r:id="rId1"/>
@@ -3413,7 +3465,7 @@
     <hyperlink ref="O30" r:id="rId23"/>
     <hyperlink ref="O32" r:id="rId24"/>
     <hyperlink ref="O34" r:id="rId25"/>
-    <hyperlink ref="O35" r:id="rId26"/>
+    <hyperlink ref="O36" r:id="rId26"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId27"/>
